--- a/artfynd/A 15110-2021 artfynd.xlsx
+++ b/artfynd/A 15110-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15110-2021 artfynd.xlsx
+++ b/artfynd/A 15110-2021 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>103579725</v>
       </c>
       <c r="B4" t="n">
-        <v>90181</v>
+        <v>90191</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 15110-2021 artfynd.xlsx
+++ b/artfynd/A 15110-2021 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>103579725</v>
       </c>
       <c r="B4" t="n">
-        <v>90191</v>
+        <v>90203</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 15110-2021 artfynd.xlsx
+++ b/artfynd/A 15110-2021 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>103579725</v>
       </c>
       <c r="B4" t="n">
-        <v>90203</v>
+        <v>90204</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 15110-2021 artfynd.xlsx
+++ b/artfynd/A 15110-2021 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>103579725</v>
       </c>
       <c r="B4" t="n">
-        <v>90204</v>
+        <v>90207</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 15110-2021 artfynd.xlsx
+++ b/artfynd/A 15110-2021 artfynd.xlsx
@@ -902,11 +902,11 @@
         <v>103579725</v>
       </c>
       <c r="B4" t="n">
-        <v>90207</v>
+        <v>90213</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dialog hos rapportör</t>
+          <t>Dialog hos validator</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/artfynd/A 15110-2021 artfynd.xlsx
+++ b/artfynd/A 15110-2021 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>103579725</v>
       </c>
       <c r="B4" t="n">
-        <v>90213</v>
+        <v>90214</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
